--- a/data/trans_bre/P2A_senso_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,58</t>
+          <t>-2,1; 0,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,52</t>
+          <t>-1,1; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,26</t>
+          <t>-1,4; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,59</t>
+          <t>0,59; 4,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 23,0</t>
+          <t>-50,68; 24,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 104,62</t>
+          <t>-38,1; 104,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,73; 128,68</t>
+          <t>-59,51; 158,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 221,52</t>
+          <t>11,48; 224,03</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,03</t>
+          <t>-0,3; 1,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,06</t>
+          <t>-0,82; 1,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,7</t>
+          <t>-0,51; 0,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 34,51</t>
+          <t>-0,01; 31,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 215,59</t>
+          <t>-33,16; 219,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 96,87</t>
+          <t>-41,18; 96,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,07; 122,29</t>
+          <t>-42,01; 123,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1869,63</t>
+          <t>-1,12; 1671,48</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,51</t>
+          <t>-0,9; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,29</t>
+          <t>-0,2; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,52</t>
+          <t>-1,12; 0,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,93</t>
+          <t>-1,55; 0,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-88,0; 846,57</t>
+          <t>-87,09; 751,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 769,74</t>
+          <t>-28,12; 669,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,66; 89,41</t>
+          <t>-59,95; 79,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,71</t>
+          <t>-0,51; 0,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,2</t>
+          <t>-0,18; 1,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,58</t>
+          <t>-0,45; 0,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 23,36</t>
+          <t>0,52; 22,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 56,33</t>
+          <t>-28,66; 58,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 84,73</t>
+          <t>-8,67; 86,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 78,72</t>
+          <t>-36,97; 67,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 1140,78</t>
+          <t>20,81; 1122,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,55</t>
+          <t>-2,16; 0,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,45</t>
+          <t>-1,06; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,33</t>
+          <t>-1,3; 1,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,64</t>
+          <t>1,09; 5,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 24,17</t>
+          <t>-51,24; 26,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 104,74</t>
+          <t>-36,28; 110,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 158,96</t>
+          <t>-55,17; 149,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 224,03</t>
+          <t>21,21; 242,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>442,39%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,02</t>
+          <t>-0,29; 0,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,06</t>
+          <t>-0,63; 1,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,72</t>
+          <t>-0,53; 0,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 31,66</t>
+          <t>-0,88; 1,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 219,48</t>
+          <t>-33,61; 208,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 96,79</t>
+          <t>-34,66; 98,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,01; 123,54</t>
+          <t>-46,47; 134,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1671,48</t>
+          <t>-28,81; 53,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-11,92%</t>
+          <t>-0,29%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,48</t>
+          <t>-0,94; 1,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,51</t>
+          <t>-0,32; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,39</t>
+          <t>-1,25; 0,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,88</t>
+          <t>-1,21; 1,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 751,62</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 669,31</t>
+          <t>-29,37; 908,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 79,26</t>
+          <t>-49,26; 113,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>281,41%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,74</t>
+          <t>-0,48; 0,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,15</t>
+          <t>-0,28; 1,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,52</t>
+          <t>-0,52; 0,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 22,98</t>
+          <t>0,03; 1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 58,47</t>
+          <t>-26,27; 57,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 86,18</t>
+          <t>-15,08; 81,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 67,85</t>
+          <t>-38,9; 74,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 1122,03</t>
+          <t>0,52; 75,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
